--- a/student-attendance/scripts/ACs/AcademicCoordinators.xlsx
+++ b/student-attendance/scripts/ACs/AcademicCoordinators.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PROJECT\Attendence-Application\student-attendance\scripts\ACs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{61CBCF0B-173C-49C9-B5BF-BD3516D33EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DB7C88-177C-4C2B-86B5-213B968882CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -55,9 +55,6 @@
     <t>5</t>
   </si>
   <si>
-    <t>MECHATRONICS</t>
-  </si>
-  <si>
     <t>CHEMICAL</t>
   </si>
   <si>
@@ -122,6 +119,9 @@
   </si>
   <si>
     <t>Dept</t>
+  </si>
+  <si>
+    <t>MCT</t>
   </si>
 </sst>
 </file>
@@ -520,7 +520,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
@@ -528,7 +528,7 @@
         <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>3</v>
@@ -536,12 +536,12 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.3">
@@ -549,7 +549,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>5</v>
@@ -557,12 +557,12 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
@@ -570,7 +570,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>7</v>
@@ -578,7 +578,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
@@ -586,7 +586,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>9</v>
@@ -594,7 +594,7 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.3">
@@ -602,56 +602,56 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C15" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="C16" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="B17" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="C20" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -661,7 +661,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A2 A20:B20 A1:B1 A4:B4 A3 A7:B7 A6 A10 A9 A12 A11 C10 A8 C8 A5 C5 C2 A14:C15 A13 C12 A19:B19 A18 C18 A17 C17 A16:B16" numberStoredAsText="1"/>
+    <ignoredError sqref="A2 A20:B20 A1:B1 A4:B4 A3 A7:B7 A6 A10 A9 A12 A11 C10 A8 C8 A5 C5 C2 A14:C15 A13 A19:B19 A18 C18 A17 C17 A16:B16" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>